--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20261008.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20261008.xlsx
@@ -755,17 +755,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>NVT US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>nVent Electric PLC</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>114,066</t>
+          <t>59,759</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -777,17 +777,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>NVT US</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>nVent Electric PLC</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>59,759</t>
+          <t>114,066</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>51,910</t>
+          <t>47,627</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>47,627</t>
+          <t>51,910</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>ITRI US</t>
+          <t>BELFB US</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>英特隆公司</t>
+          <t>百富電子有限公司</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>8,121</t>
+          <t>2,839</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>BELFB US</t>
+          <t>ITRI US</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>百富電子有限公司</t>
+          <t>英特隆公司</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>2,839</t>
+          <t>8,121</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
